--- a/GHG_Trajectory_Analysis_Study/outputs/tables/Sensitivity Analysis_Sample Composition.xlsx
+++ b/GHG_Trajectory_Analysis_Study/outputs/tables/Sensitivity Analysis_Sample Composition.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Headline holds (&gt;50% SDG 13.2-Critical)</t>
+          <t>Headline holds (&gt;50% Rapidly Rising)</t>
         </is>
       </c>
     </row>
